--- a/Zinc/5. Cluster analysis/Clustering by sample results/Sites_with_many_typologies.xlsx
+++ b/Zinc/5. Cluster analysis/Clustering by sample results/Sites_with_many_typologies.xlsx
@@ -1,166 +1,173 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://irtacat-my.sharepoint.com/personal/cecilia_albert_irta_cat/Documents/Escriptori/Trace-element-bioavailability-spatial-assessment/Zinc/5. Cluster analysis/Clustering by sample results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_EF32B3280059E8E15F05D6685DBE079392598CC7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3772C7D0-89E3-4F65-AD9C-139FB5F1EEDA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sites" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sites" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_typologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">typologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCK0.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial, Developed Perennial, Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial, Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial, Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial, Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downtown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial, Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK13.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK16.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK18.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK7.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial, Developed Perennial, Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial, Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial, Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial, Perennial, Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial, Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinhook Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial, Perennial, Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>n_typologies</t>
+  </si>
+  <si>
+    <t>typologies</t>
+  </si>
+  <si>
+    <t>BCK0.9</t>
+  </si>
+  <si>
+    <t>Perennial, Developed Perennial, Main Stem</t>
+  </si>
+  <si>
+    <t>BSL1.1</t>
+  </si>
+  <si>
+    <t>Developed Perennial, Main Stem</t>
+  </si>
+  <si>
+    <t>BSL1.3</t>
+  </si>
+  <si>
+    <t>BSL2.2</t>
+  </si>
+  <si>
+    <t>BSL2.3</t>
+  </si>
+  <si>
+    <t>Perennial, Developed Perennial</t>
+  </si>
+  <si>
+    <t>BSL3.1</t>
+  </si>
+  <si>
+    <t>BSL3.2</t>
+  </si>
+  <si>
+    <t>BSL3.3</t>
+  </si>
+  <si>
+    <t>BSL4.1</t>
+  </si>
+  <si>
+    <t>Perennial, Pooled</t>
+  </si>
+  <si>
+    <t>BSL4.2</t>
+  </si>
+  <si>
+    <t>BSL4.3</t>
+  </si>
+  <si>
+    <t>Downtown</t>
+  </si>
+  <si>
+    <t>EFK10.0</t>
+  </si>
+  <si>
+    <t>Perennial, Main Stem</t>
+  </si>
+  <si>
+    <t>EFK13.8</t>
+  </si>
+  <si>
+    <t>EFK16.2</t>
+  </si>
+  <si>
+    <t>EFK18.2</t>
+  </si>
+  <si>
+    <t>EFK2.0</t>
+  </si>
+  <si>
+    <t>EFK20</t>
+  </si>
+  <si>
+    <t>EFK5.4</t>
+  </si>
+  <si>
+    <t>EFK7.9</t>
+  </si>
+  <si>
+    <t>MCA1</t>
+  </si>
+  <si>
+    <t>MCA3.1</t>
+  </si>
+  <si>
+    <t>Perennial, Developed Perennial, Pooled</t>
+  </si>
+  <si>
+    <t>MCA3.2</t>
+  </si>
+  <si>
+    <t>Non-Perennial, Pooled</t>
+  </si>
+  <si>
+    <t>MCA4</t>
+  </si>
+  <si>
+    <t>MTN1.1</t>
+  </si>
+  <si>
+    <t>Developed Perennial, Pooled</t>
+  </si>
+  <si>
+    <t>MTN4</t>
+  </si>
+  <si>
+    <t>Non-Perennial, Perennial, Developed Perennial</t>
+  </si>
+  <si>
+    <t>NBO2</t>
+  </si>
+  <si>
+    <t>NBO3</t>
+  </si>
+  <si>
+    <t>Non-Perennial, Perennial</t>
+  </si>
+  <si>
+    <t>NBO5</t>
+  </si>
+  <si>
+    <t>Pinhook Branch</t>
+  </si>
+  <si>
+    <t>WBK1</t>
+  </si>
+  <si>
+    <t>WBK2</t>
+  </si>
+  <si>
+    <t>Non-Perennial, Perennial, Pooled</t>
+  </si>
+  <si>
+    <t>WBK3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -196,6 +203,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -477,11 +493,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -492,363 +512,363 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>2</v>
       </c>
       <c r="C26" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>3</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>38</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>3</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>39</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>41</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>42</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>43</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>44</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>46</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
@@ -857,6 +877,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>